--- a/data/metadata_raw/air_pollutant_emissions.xlsx
+++ b/data/metadata_raw/air_pollutant_emissions.xlsx
@@ -521,7 +521,7 @@
     <t>2022-09-15</t>
   </si>
   <si>
-    <t>2024-08-23</t>
+    <t>2025-06-30</t>
   </si>
   <si>
     <t>3.02.02.0001</t>
